--- a/liveprices.xlsx
+++ b/liveprices.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sweety\Documents\live-price\live-price\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\techsupport\Documents\GitHub\live-prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7D6567-46DD-4F03-902D-E45067C95CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52C453F-25FF-40A3-A2F5-26286E7F17E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2BE2BCF-E914-407A-8B63-14456AB7C56A}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Symbol</t>
   </si>
@@ -160,6 +160,21 @@
   </si>
   <si>
     <t>TESLA</t>
+  </si>
+  <si>
+    <t>US30ROLL</t>
+  </si>
+  <si>
+    <t>US500ROLL</t>
+  </si>
+  <si>
+    <t>US500H6</t>
+  </si>
+  <si>
+    <t>USDINDEXH6</t>
+  </si>
+  <si>
+    <t>GCG6</t>
   </si>
 </sst>
 </file>
@@ -335,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -390,7 +405,6 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -417,133 +431,140 @@
       <ddeItem name="ALIBABA" advise="1">
         <values>
           <value>
-            <val>124.202</val>
+            <val>162.18199999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="ALPHABET-A" advise="1">
         <values>
           <value>
-            <val>208.346</val>
+            <val>321.74099999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AMAZON" advise="1">
         <values>
           <value>
-            <val>227.72499999999999</val>
+            <val>230.899</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="APPLE" advise="1">
         <values>
           <value>
-            <val>227.035</val>
+            <val>246.44499999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCAD" advise="1">
         <values>
           <value>
-            <val>0.89771000000000001</val>
+            <val>0.93372999999999995</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCHF" advise="1">
         <values>
           <value>
-            <val>0.52251999999999998</val>
+            <val>0.53420999999999996</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDNZD" advise="1">
         <values>
           <value>
-            <val>1.1091800000000001</val>
+            <val>1.15388</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDUSD" advise="1">
         <values>
           <value>
-            <val>0.64778000000000002</val>
+            <val>0.67513999999999996</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="BOEING" advise="1">
         <values>
           <value>
-            <val>226.7</val>
+            <val>248.68</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURAUD" advise="1">
         <values>
           <value>
-            <val>1.7935300000000001</val>
+            <val>1.7354099999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURCAD" advise="1">
         <values>
           <value>
-            <val>1.6103400000000001</val>
+            <val>1.62066</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURUSD" advise="1">
         <values>
           <value>
-            <val>1.1620600000000001</val>
+            <val>1.17187</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPCHF" advise="1">
         <values>
           <value>
-            <val>1.0851999999999999</val>
+            <val>1.06368</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPUSD" advise="1">
         <values>
           <value>
-            <val>1.34541</val>
+            <val>1.3442499999999999</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="Gold.feb6" advise="1">
+        <values>
+          <value>
+            <val>4835.21</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MICROSOFT" advise="1">
         <values>
           <value>
-            <val>504.07400000000001</val>
+            <val>454.28500000000003</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MODERNA" advise="1">
         <values>
           <value>
-            <val>25.222999999999999</val>
+            <val>42.872999999999998</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NETFLIX" advise="1">
         <values>
           <value>
-            <val>1217.847</val>
+            <val>86.972999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NVIDIA" advise="1">
         <values>
           <value>
-            <val>179.67500000000001</val>
+            <val>177.89699999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NZDUSD" advise="1">
         <values>
           <value>
-            <val>0.58384000000000003</val>
+            <val>0.58494000000000002</val>
           </value>
         </values>
       </ddeItem>
@@ -551,56 +572,77 @@
       <ddeItem name="TESLA" advise="1">
         <values>
           <value>
-            <val>346.40499999999997</val>
+            <val>419.03199999999998</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US30.CASH" advise="1">
+        <values>
+          <value>
+            <val>48589.16</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.CASH" advise="1">
+        <values>
+          <value>
+            <val>6821.93</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.MAR6" advise="1">
+        <values>
+          <value>
+            <val>6855.61</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCAD" advise="1">
         <values>
           <value>
-            <val>1.38581</val>
+            <val>1.3830499999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCHF" advise="1">
         <values>
           <value>
-            <val>0.80659999999999998</val>
+            <val>0.79129000000000005</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDJPY" advise="1">
         <values>
           <value>
-            <val>147.78200000000001</val>
-          </value>
-        </values>
-      </ddeItem>
-      <ddeItem name="WTI" advise="1">
-        <values>
-          <value t="str">
-            <val>N\A</val>
+            <val>158.02600000000001</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="USNDX.MAR6" advise="1">
+        <values>
+          <value>
+            <val>25240.77</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAGUSD" advise="1">
         <values>
           <value>
-            <val>38.698</val>
+            <val>94.453999999999994</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAUUSD" advise="1">
         <values>
           <value>
-            <val>3376.32</val>
+            <val>4832.6000000000004</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XPTUSD" advise="1">
         <values>
           <value>
-            <val>1341.62</val>
+            <val>2442.62</val>
           </value>
         </values>
       </ddeItem>
@@ -616,133 +658,140 @@
       <ddeItem name="ALIBABA" advise="1">
         <values>
           <value>
-            <val>124.488</val>
+            <val>162.47800000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="ALPHABET-A" advise="1">
         <values>
           <value>
-            <val>208.64599999999999</val>
+            <val>322.09100000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AMAZON" advise="1">
         <values>
           <value>
-            <val>228.05500000000001</val>
+            <val>231.279</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="APPLE" advise="1">
         <values>
           <value>
-            <val>227.345</val>
+            <val>246.905</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCAD" advise="1">
         <values>
           <value>
-            <val>0.89800000000000002</val>
+            <val>0.93405000000000005</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCHF" advise="1">
         <values>
           <value>
-            <val>0.52278999999999998</val>
+            <val>0.53449999999999998</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDNZD" advise="1">
         <values>
           <value>
-            <val>1.1096999999999999</val>
+            <val>1.1544099999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDUSD" advise="1">
         <values>
           <value>
-            <val>0.64795999999999998</val>
+            <val>0.67530000000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="BOEING" advise="1">
         <values>
           <value>
-            <val>227.11</val>
+            <val>249.09</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURAUD" advise="1">
         <values>
           <value>
-            <val>1.79392</val>
+            <val>1.7357800000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURCAD" advise="1">
         <values>
           <value>
-            <val>1.6107400000000001</val>
+            <val>1.6211</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURUSD" advise="1">
         <values>
           <value>
-            <val>1.1621900000000001</val>
+            <val>1.1719599999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPCHF" advise="1">
         <values>
           <value>
-            <val>1.0856600000000001</val>
+            <val>1.06412</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPUSD" advise="1">
         <values>
           <value>
-            <val>1.3455999999999999</val>
+            <val>1.3444</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="GOLD.FEB6" advise="1">
+        <values>
+          <value>
+            <val>4835.68</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MICROSOFT" advise="1">
         <values>
           <value>
-            <val>504.43400000000003</val>
+            <val>454.86500000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MODERNA" advise="1">
         <values>
           <value>
-            <val>25.497</val>
+            <val>43.137</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NETFLIX" advise="1">
         <values>
           <value>
-            <val>1218.377</val>
+            <val>87.263000000000005</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NVIDIA" advise="1">
         <values>
           <value>
-            <val>179.95500000000001</val>
+            <val>178.18700000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NZDUSD" advise="1">
         <values>
           <value>
-            <val>0.58411000000000002</val>
+            <val>0.58518000000000003</val>
           </value>
         </values>
       </ddeItem>
@@ -750,49 +799,77 @@
       <ddeItem name="TESLA" advise="1">
         <values>
           <value>
-            <val>346.80500000000001</val>
+            <val>419.392</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US30.CASH" advise="1">
+        <values>
+          <value>
+            <val>48591.18</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.CASH" advise="1">
+        <values>
+          <value>
+            <val>6822.46</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.MAR6" advise="1">
+        <values>
+          <value>
+            <val>6856.73</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCAD" advise="1">
         <values>
           <value>
-            <val>1.38605</val>
+            <val>1.3832800000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCHF" advise="1">
         <values>
           <value>
-            <val>0.80681999999999998</val>
+            <val>0.79149000000000003</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDJPY" advise="1">
         <values>
           <value>
-            <val>147.80099999999999</val>
+            <val>158.035</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="USNDX.MAR6" advise="1">
+        <values>
+          <value>
+            <val>25243.040000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAGUSD" advise="1">
         <values>
           <value>
-            <val>38.726999999999997</val>
+            <val>94.497</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAUUSD" advise="1">
         <values>
           <value>
-            <val>3376.55</val>
+            <val>4833</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XPTUSD" advise="1">
         <values>
           <value>
-            <val>1343.84</val>
+            <val>2453</val>
           </value>
         </values>
       </ddeItem>
@@ -808,126 +885,133 @@
       <ddeItem name="ALIBABA" advise="1">
         <values>
           <value>
-            <val>123.381</val>
+            <val>160.78399999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="ALPHABET-A" advise="1">
         <values>
           <value>
-            <val>205.11500000000001</val>
+            <val>317.435</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AMAZON" advise="1">
         <values>
           <value>
-            <val>226.89500000000001</val>
+            <val>229.167</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="APPLE" advise="1">
         <values>
           <value>
-            <val>225.9</val>
+            <val>243.279</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCAD" advise="1">
         <values>
           <value>
-            <val>0.89656999999999998</val>
+            <val>0.93088000000000004</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCHF" advise="1">
         <values>
           <value>
-            <val>0.52056000000000002</val>
+            <val>0.53144999999999998</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDNZD" advise="1">
         <values>
           <value>
-            <val>1.10728</val>
+            <val>1.1532199999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDUSD" advise="1">
         <values>
           <value>
-            <val>0.64688999999999997</val>
+            <val>0.67266999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="BOEING" advise="1">
         <values>
           <value>
-            <val>226.47</val>
+            <val>242.87</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURAUD" advise="1">
         <values>
           <value>
-            <val>1.79149</val>
+            <val>1.7347999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURCAD" advise="1">
         <values>
           <value>
-            <val>1.6091800000000001</val>
+            <val>1.6202399999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURUSD" advise="1">
         <values>
           <value>
-            <val>1.1609499999999999</val>
+            <val>1.1709499999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPCHF" advise="1">
         <values>
           <value>
-            <val>1.0823400000000001</val>
+            <val>1.0610200000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPUSD" advise="1">
         <values>
           <value>
-            <val>1.3445</val>
+            <val>1.3428800000000001</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="Gold.feb6" advise="1">
+        <values>
+          <value>
+            <val>4774.3599999999997</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MICROSOFT" advise="1">
         <values>
           <value>
-            <val>503.12099999999998</val>
+            <val>445.35300000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MODERNA" advise="1">
         <values>
           <value>
-            <val>25.22</val>
+            <val>40.781999999999996</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NETFLIX" advise="1">
         <values>
           <value>
-            <val>1198.308</val>
+            <val>86.891999999999996</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NVIDIA" advise="1">
         <values>
           <value>
-            <val>176.42099999999999</val>
+            <val>177.535</val>
           </value>
         </values>
       </ddeItem>
@@ -935,42 +1019,70 @@
       <ddeItem name="TESLA" advise="1">
         <values>
           <value>
-            <val>334.875</val>
+            <val>417.29199999999997</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US30.CASH" advise="1">
+        <values>
+          <value>
+            <val>48515.16</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.CASH" advise="1">
+        <values>
+          <value>
+            <val>6798.96</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.MAR6" advise="1">
+        <values>
+          <value>
+            <val>6832.54</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCHF" advise="1">
         <values>
           <value>
-            <val>0.80264000000000002</val>
+            <val>0.78886999999999996</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDJPY" advise="1">
         <values>
           <value>
-            <val>146.976</val>
+            <val>157.85400000000001</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="USNDX.MAR6" advise="1">
+        <values>
+          <value>
+            <val>25117.49</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAGUSD" advise="1">
         <values>
           <value>
-            <val>38.326999999999998</val>
+            <val>93.344999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAUUSD" advise="1">
         <values>
           <value>
-            <val>3351.33</val>
+            <val>4770.58</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XPTUSD" advise="1">
         <values>
           <value>
-            <val>1336.97</val>
+            <val>2413.29</val>
           </value>
         </values>
       </ddeItem>
@@ -986,84 +1098,84 @@
       <ddeItem name="ALIBABA" advise="1">
         <values>
           <value>
-            <val>126.574</val>
+            <val>165.953</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="ALPHABET-A" advise="1">
         <values>
           <value>
-            <val>210.36500000000001</val>
+            <val>327.56099999999998</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AMAZON" advise="1">
         <values>
           <value>
-            <val>229.44499999999999</val>
+            <val>234.94300000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="APPLE" advise="1">
         <values>
           <value>
-            <val>229.14500000000001</val>
+            <val>254.614</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCAD" advise="1">
         <values>
           <value>
-            <val>0.89912000000000003</val>
+            <val>0.93384999999999996</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCHF" advise="1">
         <values>
           <value>
-            <val>0.52268000000000003</val>
+            <val>0.53447</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDNZD" advise="1">
         <values>
           <value>
-            <val>1.11032</val>
+            <val>1.15611</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDUSD" advise="1">
         <values>
           <value>
-            <val>0.64927000000000001</val>
+            <val>0.67523</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="BOEING" advise="1">
         <values>
           <value>
-            <val>230.06299999999999</val>
+            <val>249.38200000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURAUD" advise="1">
         <values>
           <value>
-            <val>1.7979799999999999</val>
+            <val>1.7418100000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURCAD" advise="1">
         <values>
           <value>
-            <val>1.61375</val>
+            <val>1.6222300000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURUSD" advise="1">
         <values>
           <value>
-            <val>1.16594</val>
+            <val>1.1733899999999999</val>
           </value>
         </values>
       </ddeItem>
@@ -1077,49 +1189,56 @@
       <ddeItem name="GBPCHF" advise="1">
         <values>
           <value>
-            <val>1.08571</val>
+            <val>1.06375</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPUSD" advise="1">
         <values>
           <value>
-            <val>1.3489599999999999</val>
+            <val>1.34558</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="Gold.feb6" advise="1">
+        <values>
+          <value>
+            <val>4890.46</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MICROSOFT" advise="1">
         <values>
           <value>
-            <val>508.01799999999997</val>
+            <val>456.61599999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MODERNA" advise="1">
         <values>
           <value>
-            <val>27.004000000000001</val>
+            <val>42.884</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NETFLIX" advise="1">
         <values>
           <value>
-            <val>1233.278</val>
+            <val>89.745999999999995</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NVIDIA" advise="1">
         <values>
           <value>
-            <val>181.76</val>
+            <val>182.17599999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NZDUSD" advise="1">
         <values>
           <value>
-            <val>0.58594999999999997</val>
+            <val>0.58499999999999996</val>
           </value>
         </values>
       </ddeItem>
@@ -1127,49 +1246,77 @@
       <ddeItem name="TESLA" advise="1">
         <values>
           <value>
-            <val>349.34500000000003</val>
+            <val>430.17700000000002</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="us30.cash" advise="1">
+        <values>
+          <value>
+            <val>48605.27</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.CASH" advise="1">
+        <values>
+          <value>
+            <val>6822.42</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.MAR6" advise="1">
+        <values>
+          <value>
+            <val>6856.08</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCAD" advise="1">
         <values>
           <value>
-            <val>1.38645</val>
+            <val>1.3839600000000001</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCHF" advise="1">
         <values>
           <value>
-            <val>0.80667999999999995</val>
+            <val>0.79178999999999999</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDJPY" advise="1">
         <values>
           <value>
-            <val>147.88</val>
+            <val>158.27699999999999</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="USNDX.MAR6" advise="1">
+        <values>
+          <value>
+            <val>25243.42</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAGUSD" advise="1">
         <values>
           <value>
-            <val>38.838999999999999</val>
+            <val>95.55</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAUUSD" advise="1">
         <values>
           <value>
-            <val>3386.55</val>
+            <val>4888.16</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XPTUSD" advise="1">
         <values>
           <value>
-            <val>1352.31</val>
+            <val>2514.64</val>
           </value>
         </values>
       </ddeItem>
@@ -1185,133 +1332,140 @@
       <ddeItem name="ALIBABA" advise="1">
         <values>
           <value>
-            <val>45894.833321759259</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="ALPHABET-A" advise="1">
         <values>
           <value>
-            <val>45894.833321759259</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AMAZON" advise="1">
         <values>
           <value>
-            <val>45894.833321759259</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="APPLE" advise="1">
         <values>
           <value>
-            <val>45894.833321759259</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCAD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.305844907409</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCHF" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306064814817</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDNZD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.305949074071</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDUSD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306030092594</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="BOEING" advise="1">
         <values>
           <value>
-            <val>45894.833298611113</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURAUD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306076388886</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURCAD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306076388886</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURUSD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306076388886</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPCHF" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306076388886</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPUSD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306064814817</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="Gold.feb6" advise="1">
+        <values>
+          <value>
+            <val>46043.306064814817</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MICROSOFT" advise="1">
         <values>
           <value>
-            <val>45894.833321759259</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MODERNA" advise="1">
         <values>
           <value>
-            <val>45894.833321759259</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NETFLIX" advise="1">
         <values>
           <value>
-            <val>45894.833321759259</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NVIDIA" advise="1">
         <values>
           <value>
-            <val>45894.833321759259</val>
+            <val>46042.874988425923</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NZDUSD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.30605324074</val>
           </value>
         </values>
       </ddeItem>
@@ -1319,42 +1473,70 @@
       <ddeItem name="TESLA" advise="1">
         <values>
           <value>
-            <val>45894.833298611113</val>
+            <val>46042.874988425923</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="us30.cash" advise="1">
+        <values>
+          <value>
+            <val>46043.306076388886</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.CASH" advise="1">
+        <values>
+          <value>
+            <val>46043.306076388886</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.MAR6" advise="1">
+        <values>
+          <value>
+            <val>46043.306076388886</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCAD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306064814817</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCHF" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306006944447</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDJPY" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306076388886</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="USNDX.MAR6" advise="1">
+        <values>
+          <value>
+            <val>46043.306064814817</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAGUSD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306076388886</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAUUSD" advise="1">
         <values>
           <value>
-            <val>45895.291747685187</val>
+            <val>46043.306064814817</val>
           </value>
         </values>
       </ddeItem>
@@ -1370,133 +1552,140 @@
       <ddeItem name="ALIBABA" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:59 124.202 124.488</val>
+            <val>2026/01/20 20:59:59 162.182 162.478</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="ALPHABET-A" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:59 208.346 208.646</val>
+            <val>2026/01/20 20:59:59 321.741 322.091</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AMAZON" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:59 227.725 228.055</val>
+            <val>2026/01/20 20:59:59 230.899 231.279</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="APPLE" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:59 227.035 227.345</val>
+            <val>2026/01/20 20:59:59 246.445 246.905</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCAD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 0.89771 0.89800</val>
+            <val>2026/01/21 07:20:25 0.93373 0.93405</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDCHF" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 0.52252 0.52279</val>
+            <val>2026/01/21 07:20:44 0.53421 0.53450</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDNZD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 1.10918 1.10970</val>
+            <val>2026/01/21 07:20:34 1.15388 1.15441</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="AUDUSD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 0.64778 0.64796</val>
+            <val>2026/01/21 07:20:41 0.67514 0.67530</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="BOEING" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:57 226.700 227.110</val>
+            <val>2026/01/20 20:59:59 248.680 249.090</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURAUD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 1.79353 1.79392</val>
+            <val>2026/01/21 07:20:45 1.73541 1.73578</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURCAD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 1.61034 1.61074</val>
+            <val>2026/01/21 07:20:45 1.62066 1.62110</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="EURUSD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 1.16206 1.16219</val>
+            <val>2026/01/21 07:20:45 1.17187 1.17196</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPCHF" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 1.08520 1.08566</val>
+            <val>2026/01/21 07:20:45 1.06368 1.06412</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="GBPUSD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 1.34541 1.34560</val>
+            <val>2026/01/21 07:20:44 1.34425 1.34440</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="Gold.feb6" advise="1">
+        <values>
+          <value t="str">
+            <val>2026/01/21 07:20:44 4835.21 4835.68</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MICROSOFT" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:59 504.074 504.434</val>
+            <val>2026/01/20 20:59:59 454.285 454.865</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="MODERNA" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:59 25.223 25.497</val>
+            <val>2026/01/20 20:59:59 42.873 43.137</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NETFLIX" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:59 1217.847 1218.377</val>
+            <val>2026/01/20 20:59:59 86.973 87.263</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NVIDIA" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:59 179.675 179.955</val>
+            <val>2026/01/20 20:59:59 177.897 178.187</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="NZDUSD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 0.58384 0.58411</val>
+            <val>2026/01/21 07:20:43 0.58494 0.58518</val>
           </value>
         </values>
       </ddeItem>
@@ -1504,42 +1693,70 @@
       <ddeItem name="TESLA" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/25 19:59:57 346.405 346.805</val>
+            <val>2026/01/20 20:59:59 419.032 419.392</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US30.CASH" advise="1">
+        <values>
+          <value t="str">
+            <val>2026/01/21 07:20:45 48589.16 48591.18</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.CASH" advise="1">
+        <values>
+          <value t="str">
+            <val>2026/01/21 07:20:45 6821.93 6822.46</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="US500.MAR6" advise="1">
+        <values>
+          <value t="str">
+            <val>2026/01/21 07:20:45 6855.61 6856.73</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCAD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 1.38581 1.38605</val>
+            <val>2026/01/21 07:20:44 1.38305 1.38328</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDCHF" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 0.80660 0.80682</val>
+            <val>2026/01/21 07:20:39 0.79129 0.79149</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="USDJPY" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 147.782 147.801</val>
+            <val>2026/01/21 07:20:45 158.026 158.035</val>
+          </value>
+        </values>
+      </ddeItem>
+      <ddeItem name="USNDX.MAR6" advise="1">
+        <values>
+          <value t="str">
+            <val>2026/01/21 07:20:44 25240.77 25243.04</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAGUSD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 38.698 38.727</val>
+            <val>2026/01/21 07:20:45 94.454 94.497</val>
           </value>
         </values>
       </ddeItem>
       <ddeItem name="XAUUSD" advise="1">
         <values>
           <value t="str">
-            <val>2025/08/26 07:00:07 3376.32 3376.55</val>
+            <val>2026/01/21 07:20:44 4832.60 4833.00</val>
           </value>
         </values>
       </ddeItem>
@@ -1869,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0995C1C6-6612-4858-9C46-9028694CCC8C}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.109375" customWidth="1"/>
@@ -1911,27 +2128,27 @@
       </c>
       <c r="C2" s="28">
         <f>[1]!XAUUSD</f>
-        <v>3376.32</v>
+        <v>4832.6000000000004</v>
       </c>
       <c r="D2" s="31">
         <f>[2]!XAUUSD</f>
-        <v>3376.55</v>
+        <v>4833</v>
       </c>
       <c r="E2" s="10">
         <f>[3]!XAUUSD</f>
-        <v>3351.33</v>
+        <v>4770.58</v>
       </c>
       <c r="F2" s="29">
         <f>[4]!XAUUSD</f>
-        <v>3386.55</v>
+        <v>4888.16</v>
       </c>
       <c r="G2" s="4">
         <f>[5]!XAUUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H2" s="5" t="str">
         <f>[6]!XAUUSD</f>
-        <v>2025/08/26 07:00:07 3376.32 3376.55</v>
+        <v>2026/01/21 07:20:44 4832.60 4833.00</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -1940,27 +2157,27 @@
       </c>
       <c r="C3" s="28">
         <f>[1]!XAGUSD</f>
-        <v>38.698</v>
+        <v>94.453999999999994</v>
       </c>
       <c r="D3" s="31">
         <f>[2]!XAGUSD</f>
-        <v>38.726999999999997</v>
+        <v>94.497</v>
       </c>
       <c r="E3" s="10">
         <f>[3]!XAGUSD</f>
-        <v>38.326999999999998</v>
+        <v>93.344999999999999</v>
       </c>
       <c r="F3" s="29">
         <f>[4]!XAGUSD</f>
-        <v>38.838999999999999</v>
+        <v>95.55</v>
       </c>
       <c r="G3" s="4">
         <f>[5]!XAGUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306076388886</v>
       </c>
       <c r="H3" s="5" t="str">
         <f>[6]!XAGUSD</f>
-        <v>2025/08/26 07:00:07 38.698 38.727</v>
+        <v>2026/01/21 07:20:45 94.454 94.497</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -1969,27 +2186,27 @@
       </c>
       <c r="C4" s="3">
         <f>[1]!GBPUSD</f>
-        <v>1.34541</v>
+        <v>1.3442499999999999</v>
       </c>
       <c r="D4" s="32">
         <f>[2]!GBPUSD</f>
-        <v>1.3455999999999999</v>
+        <v>1.3444</v>
       </c>
       <c r="E4" s="10">
         <f>[3]!GBPUSD</f>
-        <v>1.3445</v>
+        <v>1.3428800000000001</v>
       </c>
       <c r="F4" s="8">
         <f>[4]!GBPUSD</f>
-        <v>1.3489599999999999</v>
+        <v>1.34558</v>
       </c>
       <c r="G4" s="4">
         <f>[5]!GBPUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H4" s="5" t="str">
         <f>[6]!GBPUSD</f>
-        <v>2025/08/26 07:00:07 1.34541 1.34560</v>
+        <v>2026/01/21 07:20:44 1.34425 1.34440</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -1998,27 +2215,27 @@
       </c>
       <c r="C5" s="6">
         <f>[1]!USDJPY</f>
-        <v>147.78200000000001</v>
+        <v>158.02600000000001</v>
       </c>
       <c r="D5" s="7">
         <f>[2]!USDJPY</f>
-        <v>147.80099999999999</v>
+        <v>158.035</v>
       </c>
       <c r="E5" s="11">
         <f>[3]!USDJPY</f>
-        <v>146.976</v>
+        <v>157.85400000000001</v>
       </c>
       <c r="F5" s="9">
         <f>[4]!USDJPY</f>
-        <v>147.88</v>
+        <v>158.27699999999999</v>
       </c>
       <c r="G5" s="4">
         <f>[5]!USDJPY</f>
-        <v>45895.291747685187</v>
+        <v>46043.306076388886</v>
       </c>
       <c r="H5" s="5" t="str">
         <f>[6]!USDJPY</f>
-        <v>2025/08/26 07:00:07 147.782 147.801</v>
+        <v>2026/01/21 07:20:45 158.026 158.035</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2027,27 +2244,27 @@
       </c>
       <c r="C6" s="14">
         <f>[1]!EURUSD</f>
-        <v>1.1620600000000001</v>
+        <v>1.17187</v>
       </c>
       <c r="D6" s="15">
         <f>[2]!EURUSD</f>
-        <v>1.1621900000000001</v>
+        <v>1.1719599999999999</v>
       </c>
       <c r="E6" s="17">
         <f>[3]!EURUSD</f>
-        <v>1.1609499999999999</v>
+        <v>1.1709499999999999</v>
       </c>
       <c r="F6" s="16">
         <f>[4]!EURUSD</f>
-        <v>1.16594</v>
+        <v>1.1733899999999999</v>
       </c>
       <c r="G6" s="18">
         <f>[5]!EURUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306076388886</v>
       </c>
       <c r="H6" s="19" t="str">
         <f>[6]!EURUSD</f>
-        <v>2025/08/26 07:00:07 1.16206 1.16219</v>
+        <v>2026/01/21 07:20:45 1.17187 1.17196</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2056,27 +2273,27 @@
       </c>
       <c r="C7">
         <f>[1]!NZDUSD</f>
-        <v>0.58384000000000003</v>
-      </c>
-      <c r="D7" s="36">
+        <v>0.58494000000000002</v>
+      </c>
+      <c r="D7" s="35">
         <f>[2]!NZDUSD</f>
-        <v>0.58411000000000002</v>
+        <v>0.58518000000000003</v>
       </c>
       <c r="E7">
         <f>[4]!NZDUSD</f>
-        <v>0.58594999999999997</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="F7">
         <f>[4]!NZDUSD</f>
-        <v>0.58594999999999997</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="G7">
         <f>[5]!NZDUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.30605324074</v>
       </c>
       <c r="H7" t="str">
         <f>[6]!NZDUSD</f>
-        <v>2025/08/26 07:00:07 0.58384 0.58411</v>
+        <v>2026/01/21 07:20:43 0.58494 0.58518</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2085,27 +2302,27 @@
       </c>
       <c r="C8" s="28">
         <f>[1]!XPTUSD</f>
-        <v>1341.62</v>
+        <v>2442.62</v>
       </c>
       <c r="D8" s="31">
         <f>[2]!XPTUSD</f>
-        <v>1343.84</v>
+        <v>2453</v>
       </c>
       <c r="E8" s="10">
         <f>[3]!XPTUSD</f>
-        <v>1336.97</v>
+        <v>2413.29</v>
       </c>
       <c r="F8" s="29">
         <f>[4]!XPTUSD</f>
-        <v>1352.31</v>
+        <v>2514.64</v>
       </c>
       <c r="G8" s="4">
         <f>[5]!XAUUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H8" s="5" t="str">
         <f>[6]!XAUUSD</f>
-        <v>2025/08/26 07:00:07 3376.32 3376.55</v>
+        <v>2026/01/21 07:20:44 4832.60 4833.00</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2114,27 +2331,27 @@
       </c>
       <c r="C9" s="20">
         <f>C2*3.75*3.67</f>
-        <v>46466.603999999999</v>
+        <v>66508.657500000001</v>
       </c>
       <c r="D9" s="21">
         <f>D2*3.75*3.67</f>
-        <v>46469.769374999996</v>
+        <v>66514.162500000006</v>
       </c>
       <c r="E9" s="23">
         <f>E2*3.75*3.67</f>
-        <v>46122.679124999995</v>
+        <v>65655.107250000001</v>
       </c>
       <c r="F9" s="22">
         <f>F2*3.75*3.67</f>
-        <v>46607.394374999996</v>
+        <v>67273.301999999996</v>
       </c>
       <c r="G9" s="24">
         <f>G2</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H9" s="25" t="str">
         <f>H2</f>
-        <v>2025/08/26 07:00:07 3376.32 3376.55</v>
+        <v>2026/01/21 07:20:44 4832.60 4833.00</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2143,27 +2360,27 @@
       </c>
       <c r="C10" s="20">
         <f>[1]!APPLE</f>
-        <v>227.035</v>
+        <v>246.44499999999999</v>
       </c>
       <c r="D10" s="21">
         <f>[2]!APPLE</f>
-        <v>227.345</v>
+        <v>246.905</v>
       </c>
       <c r="E10" s="23">
         <f>[3]!APPLE</f>
-        <v>225.9</v>
+        <v>243.279</v>
       </c>
       <c r="F10" s="22">
         <f>[4]!APPLE</f>
-        <v>229.14500000000001</v>
+        <v>254.614</v>
       </c>
       <c r="G10" s="24">
         <f>[5]!APPLE</f>
-        <v>45894.833321759259</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H10" s="25" t="str">
         <f>[6]!APPLE</f>
-        <v>2025/08/25 19:59:59 227.035 227.345</v>
+        <v>2026/01/20 20:59:59 246.445 246.905</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2172,11 +2389,11 @@
       </c>
       <c r="C11">
         <f>[1]!USDCAD</f>
-        <v>1.38581</v>
+        <v>1.3830499999999999</v>
       </c>
       <c r="D11">
         <f>[2]!USDCAD</f>
-        <v>1.38605</v>
+        <v>1.3832800000000001</v>
       </c>
       <c r="E11" t="str">
         <f>[4]!F11USDCAD</f>
@@ -2184,15 +2401,15 @@
       </c>
       <c r="F11">
         <f>[4]!USDCAD</f>
-        <v>1.38645</v>
-      </c>
-      <c r="G11" s="35">
+        <v>1.3839600000000001</v>
+      </c>
+      <c r="G11" s="34">
         <f>[5]!USDCAD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H11" t="str">
         <f>[6]!USDCAD</f>
-        <v>2025/08/26 07:00:07 1.38581 1.38605</v>
+        <v>2026/01/21 07:20:44 1.38305 1.38328</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2201,27 +2418,27 @@
       </c>
       <c r="C12">
         <f>[1]!USDCHF</f>
-        <v>0.80659999999999998</v>
+        <v>0.79129000000000005</v>
       </c>
       <c r="D12">
         <f>[2]!USDCHF</f>
-        <v>0.80681999999999998</v>
+        <v>0.79149000000000003</v>
       </c>
       <c r="E12">
         <f>[3]!USDCHF</f>
-        <v>0.80264000000000002</v>
+        <v>0.78886999999999996</v>
       </c>
       <c r="F12">
         <f>[4]!USDCHF</f>
-        <v>0.80667999999999995</v>
+        <v>0.79178999999999999</v>
       </c>
       <c r="G12">
         <f>[5]!USDCHF</f>
-        <v>45895.291747685187</v>
+        <v>46043.306006944447</v>
       </c>
       <c r="H12" t="str">
         <f>[6]!USDCHF</f>
-        <v>2025/08/26 07:00:07 0.80660 0.80682</v>
+        <v>2026/01/21 07:20:39 0.79129 0.79149</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2230,27 +2447,27 @@
       </c>
       <c r="C13">
         <f>[1]!GBPCHF</f>
-        <v>1.0851999999999999</v>
+        <v>1.06368</v>
       </c>
       <c r="D13">
         <f>[2]!GBPCHF</f>
-        <v>1.0856600000000001</v>
+        <v>1.06412</v>
       </c>
       <c r="E13">
         <f>[3]!GBPCHF</f>
-        <v>1.0823400000000001</v>
+        <v>1.0610200000000001</v>
       </c>
       <c r="F13">
         <f>[4]!GBPCHF</f>
-        <v>1.08571</v>
+        <v>1.06375</v>
       </c>
       <c r="G13">
         <f>[5]!GBPCHF</f>
-        <v>45895.291747685187</v>
+        <v>46043.306076388886</v>
       </c>
       <c r="H13" t="str">
         <f>[6]!GBPCHF</f>
-        <v>2025/08/26 07:00:07 1.08520 1.08566</v>
+        <v>2026/01/21 07:20:45 1.06368 1.06412</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2259,27 +2476,27 @@
       </c>
       <c r="C14" s="28">
         <f>C3*32.1507</f>
-        <v>1244.1677886</v>
+        <v>3036.7622177999997</v>
       </c>
       <c r="D14" s="31">
         <f>D3*32.1507</f>
-        <v>1245.1001589</v>
+        <v>3038.1446979000002</v>
       </c>
       <c r="E14" s="10">
         <f>E3*32.1507</f>
-        <v>1232.2398788999999</v>
+        <v>3001.1070915</v>
       </c>
       <c r="F14" s="29">
         <f>F3*32.1507</f>
-        <v>1248.7010373000001</v>
+        <v>3071.9993850000001</v>
       </c>
       <c r="G14" s="4">
         <f>[5]!XAGUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306076388886</v>
       </c>
       <c r="H14" s="5" t="str">
         <f>[6]!XAGUSD</f>
-        <v>2025/08/26 07:00:07 38.698 38.727</v>
+        <v>2026/01/21 07:20:45 94.454 94.497</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2288,27 +2505,27 @@
       </c>
       <c r="C15">
         <f>[1]!AUDUSD</f>
-        <v>0.64778000000000002</v>
+        <v>0.67513999999999996</v>
       </c>
       <c r="D15">
         <f>[2]!AUDUSD</f>
-        <v>0.64795999999999998</v>
+        <v>0.67530000000000001</v>
       </c>
       <c r="E15">
         <f>[3]!AUDUSD</f>
-        <v>0.64688999999999997</v>
+        <v>0.67266999999999999</v>
       </c>
       <c r="F15">
         <f>[4]!AUDUSD</f>
-        <v>0.64927000000000001</v>
+        <v>0.67523</v>
       </c>
       <c r="G15">
         <f>[5]!AUDUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306030092594</v>
       </c>
       <c r="H15" t="str">
         <f>[6]!AUDUSD</f>
-        <v>2025/08/26 07:00:07 0.64778 0.64796</v>
+        <v>2026/01/21 07:20:41 0.67514 0.67530</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2317,27 +2534,27 @@
       </c>
       <c r="C16">
         <f>[1]!EURCAD</f>
-        <v>1.6103400000000001</v>
+        <v>1.62066</v>
       </c>
       <c r="D16">
         <f>[2]!EURCAD</f>
-        <v>1.6107400000000001</v>
+        <v>1.6211</v>
       </c>
       <c r="E16">
         <f>[3]!EURCAD</f>
-        <v>1.6091800000000001</v>
+        <v>1.6202399999999999</v>
       </c>
       <c r="F16">
         <f>[4]!EURCAD</f>
-        <v>1.61375</v>
+        <v>1.6222300000000001</v>
       </c>
       <c r="G16">
         <f>[5]!EURCAD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306076388886</v>
       </c>
       <c r="H16" t="str">
         <f>[6]!EURCAD</f>
-        <v>2025/08/26 07:00:07 1.61034 1.61074</v>
+        <v>2026/01/21 07:20:45 1.62066 1.62110</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2346,27 +2563,27 @@
       </c>
       <c r="C17">
         <f>[1]!EURAUD</f>
-        <v>1.7935300000000001</v>
+        <v>1.7354099999999999</v>
       </c>
       <c r="D17">
         <f>[2]!EURAUD</f>
-        <v>1.79392</v>
+        <v>1.7357800000000001</v>
       </c>
       <c r="E17">
         <f>[3]!EURAUD</f>
-        <v>1.79149</v>
+        <v>1.7347999999999999</v>
       </c>
       <c r="F17">
         <f>[4]!EURAUD</f>
-        <v>1.7979799999999999</v>
+        <v>1.7418100000000001</v>
       </c>
       <c r="G17">
         <f>[5]!EURAUD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306076388886</v>
       </c>
       <c r="H17" t="str">
         <f>[6]!EURAUD</f>
-        <v>2025/08/26 07:00:07 1.79353 1.79392</v>
+        <v>2026/01/21 07:20:45 1.73541 1.73578</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2375,27 +2592,27 @@
       </c>
       <c r="C18" s="28">
         <f>C2*32.1507/1000*116.64</f>
-        <v>12661.39463809536</v>
+        <v>18122.528589724803</v>
       </c>
       <c r="D18" s="31">
         <f>D2*32.1507/1000*116.64</f>
-        <v>12662.257151354401</v>
+        <v>18124.028612784001</v>
       </c>
       <c r="E18" s="10">
         <f>E2*32.1507/1000*116.64</f>
-        <v>12567.68069747184</v>
+        <v>17889.950014395839</v>
       </c>
       <c r="F18" s="29">
         <f>F2*32.1507/1000*116.64</f>
-        <v>12699.7577278344</v>
+        <v>18330.881792647677</v>
       </c>
       <c r="G18" s="4">
         <f>[5]!XAUUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H18" s="5" t="str">
         <f>[6]!XAUUSD</f>
-        <v>2025/08/26 07:00:07 3376.32 3376.55</v>
+        <v>2026/01/21 07:20:44 4832.60 4833.00</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2404,27 +2621,27 @@
       </c>
       <c r="C19">
         <f>[1]!AUDCAD</f>
-        <v>0.89771000000000001</v>
+        <v>0.93372999999999995</v>
       </c>
       <c r="D19">
         <f>[2]!AUDCAD</f>
-        <v>0.89800000000000002</v>
+        <v>0.93405000000000005</v>
       </c>
       <c r="E19">
         <f>[3]!AUDCAD</f>
-        <v>0.89656999999999998</v>
+        <v>0.93088000000000004</v>
       </c>
       <c r="F19">
         <f>[4]!AUDCAD</f>
-        <v>0.89912000000000003</v>
+        <v>0.93384999999999996</v>
       </c>
       <c r="G19">
         <f>[5]!AUDCAD</f>
-        <v>45895.291747685187</v>
+        <v>46043.305844907409</v>
       </c>
       <c r="H19" t="str">
         <f>[6]!AUDCAD</f>
-        <v>2025/08/26 07:00:07 0.89771 0.89800</v>
+        <v>2026/01/21 07:20:25 0.93373 0.93405</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2433,27 +2650,27 @@
       </c>
       <c r="C20" s="28">
         <f>C2*32.1507/1000</f>
-        <v>108.55105142400001</v>
+        <v>155.37147282000004</v>
       </c>
       <c r="D20" s="31">
         <f>D2*32.1507/1000</f>
-        <v>108.558446085</v>
+        <v>155.38433309999999</v>
       </c>
       <c r="E20" s="10">
         <f>E2*32.1507/1000</f>
-        <v>107.747605431</v>
+        <v>153.377486406</v>
       </c>
       <c r="F20" s="29">
         <f>F2*32.1507/1000</f>
-        <v>108.879953085</v>
+        <v>157.15776571199999</v>
       </c>
       <c r="G20" s="4">
         <f>[5]!XAUUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H20" s="5" t="str">
         <f>[6]!XAUUSD</f>
-        <v>2025/08/26 07:00:07 3376.32 3376.55</v>
+        <v>2026/01/21 07:20:44 4832.60 4833.00</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2462,27 +2679,27 @@
       </c>
       <c r="C21">
         <f>[1]!AUDCHF</f>
-        <v>0.52251999999999998</v>
+        <v>0.53420999999999996</v>
       </c>
       <c r="D21">
         <f>[2]!AUDCHF</f>
-        <v>0.52278999999999998</v>
+        <v>0.53449999999999998</v>
       </c>
       <c r="E21">
         <f>[3]!AUDCHF</f>
-        <v>0.52056000000000002</v>
+        <v>0.53144999999999998</v>
       </c>
       <c r="F21">
         <f>[4]!AUDCHF</f>
-        <v>0.52268000000000003</v>
+        <v>0.53447</v>
       </c>
       <c r="G21">
         <f>[5]!AUDCHF</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H21" t="str">
         <f>[6]!AUDCHF</f>
-        <v>2025/08/26 07:00:07 0.52252 0.52279</v>
+        <v>2026/01/21 07:20:44 0.53421 0.53450</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
@@ -2491,27 +2708,27 @@
       </c>
       <c r="C22">
         <f>[1]!AUDNZD</f>
-        <v>1.1091800000000001</v>
+        <v>1.15388</v>
       </c>
       <c r="D22">
         <f>[2]!AUDNZD</f>
-        <v>1.1096999999999999</v>
+        <v>1.1544099999999999</v>
       </c>
       <c r="E22">
         <f>[3]!AUDNZD</f>
-        <v>1.10728</v>
+        <v>1.1532199999999999</v>
       </c>
       <c r="F22">
         <f>[4]!AUDNZD</f>
-        <v>1.11032</v>
+        <v>1.15611</v>
       </c>
       <c r="G22">
         <f>[5]!AUDNZD</f>
-        <v>45895.291747685187</v>
+        <v>46043.305949074071</v>
       </c>
       <c r="H22" t="str">
         <f>[6]!AUDNZD</f>
-        <v>2025/08/26 07:00:07 1.10918 1.10970</v>
+        <v>2026/01/21 07:20:34 1.15388 1.15441</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2520,27 +2737,27 @@
       </c>
       <c r="C23" s="28">
         <f>C2*32.1507</f>
-        <v>108551.051424</v>
+        <v>155371.47282000002</v>
       </c>
       <c r="D23" s="31">
         <f>D2*32.1507</f>
-        <v>108558.446085</v>
+        <v>155384.33309999999</v>
       </c>
       <c r="E23" s="10">
         <f>E2*32.1507</f>
-        <v>107747.605431</v>
+        <v>153377.48640600001</v>
       </c>
       <c r="F23" s="29">
         <f>F2*32.1507</f>
-        <v>108879.953085</v>
+        <v>157157.76571199999</v>
       </c>
       <c r="G23" s="4">
         <f>[5]!XAUUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H23" s="5" t="str">
         <f>[6]!XAUUSD</f>
-        <v>2025/08/26 07:00:07 3376.32 3376.55</v>
+        <v>2026/01/21 07:20:44 4832.60 4833.00</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="32.4" x14ac:dyDescent="0.55000000000000004">
@@ -2549,295 +2766,434 @@
       </c>
       <c r="C24" s="28">
         <f>C2*31.99</f>
-        <v>108008.4768</v>
+        <v>154594.87400000001</v>
       </c>
       <c r="D24" s="31">
         <f>D2*31.99</f>
-        <v>108015.8345</v>
+        <v>154607.66999999998</v>
       </c>
       <c r="E24" s="10">
         <f>E2*31.99</f>
-        <v>107209.04669999999</v>
+        <v>152610.8542</v>
       </c>
       <c r="F24" s="29">
         <f>F2*31.99</f>
-        <v>108335.73450000001</v>
+        <v>156372.2384</v>
       </c>
       <c r="G24" s="4">
         <f>[5]!XAUUSD</f>
-        <v>45895.291747685187</v>
+        <v>46043.306064814817</v>
       </c>
       <c r="H24" s="5" t="str">
         <f>[6]!XAUUSD</f>
-        <v>2025/08/26 07:00:07 3376.32 3376.55</v>
+        <v>2026/01/21 07:20:44 4832.60 4833.00</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
       <c r="A25" s="33"/>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="33" t="s">
         <v>30</v>
       </c>
       <c r="C25">
         <f>[1]!ALIBABA</f>
-        <v>124.202</v>
+        <v>162.18199999999999</v>
       </c>
       <c r="D25">
         <f>[2]!ALIBABA</f>
-        <v>124.488</v>
+        <v>162.47800000000001</v>
       </c>
       <c r="E25">
         <f>[3]!ALIBABA</f>
-        <v>123.381</v>
+        <v>160.78399999999999</v>
       </c>
       <c r="F25">
         <f>[4]!ALIBABA</f>
-        <v>126.574</v>
+        <v>165.953</v>
       </c>
       <c r="G25">
         <f>[5]!ALIBABA</f>
-        <v>45894.833321759259</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H25" t="str">
         <f>[6]!ALIBABA</f>
-        <v>2025/08/25 19:59:59 124.202 124.488</v>
+        <v>2026/01/20 20:59:59 162.182 162.478</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="33" t="s">
         <v>31</v>
       </c>
       <c r="C26">
         <f>[1]!'ALPHABET-A'</f>
-        <v>208.346</v>
+        <v>321.74099999999999</v>
       </c>
       <c r="D26">
         <f>[2]!'ALPHABET-A'</f>
-        <v>208.64599999999999</v>
+        <v>322.09100000000001</v>
       </c>
       <c r="E26">
         <f>[3]!'ALPHABET-A'</f>
-        <v>205.11500000000001</v>
+        <v>317.435</v>
       </c>
       <c r="F26">
         <f>[4]!'ALPHABET-A'</f>
-        <v>210.36500000000001</v>
+        <v>327.56099999999998</v>
       </c>
       <c r="G26">
         <f>[5]!'ALPHABET-A'</f>
-        <v>45894.833321759259</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H26" t="str">
         <f>[6]!'ALPHABET-A'</f>
-        <v>2025/08/25 19:59:59 208.346 208.646</v>
+        <v>2026/01/20 20:59:59 321.741 322.091</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="33" t="s">
         <v>32</v>
       </c>
       <c r="C27">
         <f>[1]!AMAZON</f>
-        <v>227.72499999999999</v>
+        <v>230.899</v>
       </c>
       <c r="D27">
         <f>[2]!AMAZON</f>
-        <v>228.05500000000001</v>
+        <v>231.279</v>
       </c>
       <c r="E27">
         <f>[3]!AMAZON</f>
-        <v>226.89500000000001</v>
+        <v>229.167</v>
       </c>
       <c r="F27">
         <f>[4]!AMAZON</f>
-        <v>229.44499999999999</v>
+        <v>234.94300000000001</v>
       </c>
       <c r="G27">
         <f>[5]!AMAZON</f>
-        <v>45894.833321759259</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H27" t="str">
         <f>[6]!AMAZON</f>
-        <v>2025/08/25 19:59:59 227.725 228.055</v>
+        <v>2026/01/20 20:59:59 230.899 231.279</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="33" t="s">
         <v>33</v>
       </c>
       <c r="C28">
         <f>[1]!BOEING</f>
-        <v>226.7</v>
+        <v>248.68</v>
       </c>
       <c r="D28">
         <f>[2]!BOEING</f>
-        <v>227.11</v>
+        <v>249.09</v>
       </c>
       <c r="E28">
         <f>[3]!BOEING</f>
-        <v>226.47</v>
+        <v>242.87</v>
       </c>
       <c r="F28">
         <f>[4]!BOEING</f>
-        <v>230.06299999999999</v>
+        <v>249.38200000000001</v>
       </c>
       <c r="G28">
         <f>[5]!BOEING</f>
-        <v>45894.833298611113</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H28" t="str">
         <f>[6]!BOEING</f>
-        <v>2025/08/25 19:59:57 226.700 227.110</v>
+        <v>2026/01/20 20:59:59 248.680 249.090</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="33" t="s">
         <v>34</v>
       </c>
       <c r="C29">
         <f>[1]!MICROSOFT</f>
-        <v>504.07400000000001</v>
+        <v>454.28500000000003</v>
       </c>
       <c r="D29">
         <f>[2]!MICROSOFT</f>
-        <v>504.43400000000003</v>
+        <v>454.86500000000001</v>
       </c>
       <c r="E29">
         <f>[3]!MICROSOFT</f>
-        <v>503.12099999999998</v>
+        <v>445.35300000000001</v>
       </c>
       <c r="F29">
         <f>[4]!MICROSOFT</f>
-        <v>508.01799999999997</v>
+        <v>456.61599999999999</v>
       </c>
       <c r="G29">
         <f>[5]!MICROSOFT</f>
-        <v>45894.833321759259</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H29" t="str">
         <f>[6]!MICROSOFT</f>
-        <v>2025/08/25 19:59:59 504.074 504.434</v>
+        <v>2026/01/20 20:59:59 454.285 454.865</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="33" t="s">
         <v>35</v>
       </c>
       <c r="C30">
         <f>[1]!MODERNA</f>
-        <v>25.222999999999999</v>
+        <v>42.872999999999998</v>
       </c>
       <c r="D30">
         <f>[2]!MODERNA</f>
-        <v>25.497</v>
+        <v>43.137</v>
       </c>
       <c r="E30">
         <f>[3]!MODERNA</f>
-        <v>25.22</v>
+        <v>40.781999999999996</v>
       </c>
       <c r="F30">
         <f>[4]!MODERNA</f>
-        <v>27.004000000000001</v>
+        <v>42.884</v>
       </c>
       <c r="G30">
         <f>[5]!MODERNA</f>
-        <v>45894.833321759259</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H30" t="str">
         <f>[6]!MODERNA</f>
-        <v>2025/08/25 19:59:59 25.223 25.497</v>
+        <v>2026/01/20 20:59:59 42.873 43.137</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="33" t="s">
         <v>36</v>
       </c>
       <c r="C31">
         <f>[1]!NETFLIX</f>
-        <v>1217.847</v>
+        <v>86.972999999999999</v>
       </c>
       <c r="D31">
         <f>[2]!NETFLIX</f>
-        <v>1218.377</v>
+        <v>87.263000000000005</v>
       </c>
       <c r="E31">
         <f>[3]!NETFLIX</f>
-        <v>1198.308</v>
+        <v>86.891999999999996</v>
       </c>
       <c r="F31">
         <f>[4]!NETFLIX</f>
-        <v>1233.278</v>
+        <v>89.745999999999995</v>
       </c>
       <c r="G31">
         <f>[5]!NETFLIX</f>
-        <v>45894.833321759259</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H31" t="str">
         <f>[6]!NETFLIX</f>
-        <v>2025/08/25 19:59:59 1217.847 1218.377</v>
+        <v>2026/01/20 20:59:59 86.973 87.263</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C32">
         <f>[1]!NVIDIA</f>
-        <v>179.67500000000001</v>
+        <v>177.89699999999999</v>
       </c>
       <c r="D32">
         <f>[2]!NVIDIA</f>
-        <v>179.95500000000001</v>
+        <v>178.18700000000001</v>
       </c>
       <c r="E32">
         <f>[3]!NVIDIA</f>
-        <v>176.42099999999999</v>
+        <v>177.535</v>
       </c>
       <c r="F32">
         <f>[4]!NVIDIA</f>
-        <v>181.76</v>
+        <v>182.17599999999999</v>
       </c>
       <c r="G32">
         <f>[5]!NVIDIA</f>
-        <v>45894.833321759259</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H32" t="str">
         <f>[6]!NVIDIA</f>
-        <v>2025/08/25 19:59:59 179.675 179.955</v>
+        <v>2026/01/20 20:59:59 177.897 178.187</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="24.6" x14ac:dyDescent="0.4">
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="33" t="s">
         <v>38</v>
       </c>
       <c r="C33">
         <f>[1]!TESLA</f>
-        <v>346.40499999999997</v>
+        <v>419.03199999999998</v>
       </c>
       <c r="D33">
         <f>[2]!TESLA</f>
-        <v>346.80500000000001</v>
+        <v>419.392</v>
       </c>
       <c r="E33">
         <f>[3]!TESLA</f>
-        <v>334.875</v>
+        <v>417.29199999999997</v>
       </c>
       <c r="F33">
         <f>[4]!TESLA</f>
-        <v>349.34500000000003</v>
+        <v>430.17700000000002</v>
       </c>
       <c r="G33">
         <f>[5]!TESLA</f>
-        <v>45894.833298611113</v>
+        <v>46042.874988425923</v>
       </c>
       <c r="H33" t="str">
         <f>[6]!TESLA</f>
-        <v>2025/08/25 19:59:57 346.405 346.805</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C34" t="str">
-        <f>[1]!WTI</f>
-        <v>N\A</v>
+        <v>2026/01/20 20:59:59 419.032 419.392</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B34" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34">
+        <f>[1]!US30.CASH</f>
+        <v>48589.16</v>
+      </c>
+      <c r="D34">
+        <f>[2]!US30.CASH</f>
+        <v>48591.18</v>
+      </c>
+      <c r="E34">
+        <f>[3]!US30.CASH</f>
+        <v>48515.16</v>
+      </c>
+      <c r="F34">
+        <f>[4]!us30.cash</f>
+        <v>48605.27</v>
+      </c>
+      <c r="G34">
+        <f>[5]!us30.cash</f>
+        <v>46043.306076388886</v>
+      </c>
+      <c r="H34" t="str">
+        <f>[6]!US30.CASH</f>
+        <v>2026/01/21 07:20:45 48589.16 48591.18</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" ht="24.6" x14ac:dyDescent="0.4">
+      <c r="B35" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35">
+        <f>[1]!US500.CASH</f>
+        <v>6821.93</v>
+      </c>
+      <c r="D35">
+        <f>[2]!US500.CASH</f>
+        <v>6822.46</v>
+      </c>
+      <c r="E35">
+        <f>[3]!US500.CASH</f>
+        <v>6798.96</v>
+      </c>
+      <c r="F35">
+        <f>[4]!US500.CASH</f>
+        <v>6822.42</v>
+      </c>
+      <c r="G35">
+        <f>[5]!US500.CASH</f>
+        <v>46043.306076388886</v>
+      </c>
+      <c r="H35" t="str">
+        <f>[6]!US500.CASH</f>
+        <v>2026/01/21 07:20:45 6821.93 6822.46</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36">
+        <f>[1]!'US500.MAR6'</f>
+        <v>6855.61</v>
+      </c>
+      <c r="D36">
+        <f>[2]!'US500.MAR6'</f>
+        <v>6856.73</v>
+      </c>
+      <c r="E36">
+        <f>[3]!'US500.MAR6'</f>
+        <v>6832.54</v>
+      </c>
+      <c r="F36">
+        <f>[4]!'US500.MAR6'</f>
+        <v>6856.08</v>
+      </c>
+      <c r="G36">
+        <f>[5]!'US500.MAR6'</f>
+        <v>46043.306076388886</v>
+      </c>
+      <c r="H36" t="str">
+        <f>[6]!'US500.MAR6'</f>
+        <v>2026/01/21 07:20:45 6855.61 6856.73</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37">
+        <f>[1]!Gold.feb6</f>
+        <v>4835.21</v>
+      </c>
+      <c r="D37">
+        <f>[2]!GOLD.FEB6</f>
+        <v>4835.68</v>
+      </c>
+      <c r="E37">
+        <f>[3]!Gold.feb6</f>
+        <v>4774.3599999999997</v>
+      </c>
+      <c r="F37">
+        <f>[4]!Gold.feb6</f>
+        <v>4890.46</v>
+      </c>
+      <c r="G37">
+        <f>[5]!Gold.feb6</f>
+        <v>46043.306064814817</v>
+      </c>
+      <c r="H37" t="str">
+        <f>[6]!Gold.feb6</f>
+        <v>2026/01/21 07:20:44 4835.21 4835.68</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38">
+        <f>[1]!USNDX.MAR6</f>
+        <v>25240.77</v>
+      </c>
+      <c r="D38">
+        <f>[2]!USNDX.MAR6</f>
+        <v>25243.040000000001</v>
+      </c>
+      <c r="E38">
+        <f>[3]!USNDX.MAR6</f>
+        <v>25117.49</v>
+      </c>
+      <c r="F38">
+        <f>[4]!USNDX.MAR6</f>
+        <v>25243.42</v>
+      </c>
+      <c r="G38">
+        <f>[5]!USNDX.MAR6</f>
+        <v>46043.306064814817</v>
+      </c>
+      <c r="H38" t="str">
+        <f>[6]!USNDX.MAR6</f>
+        <v>2026/01/21 07:20:44 25240.77 25243.04</v>
       </c>
     </row>
   </sheetData>
